--- a/results/Int Task Remove ACC 0.6/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.6/Linea_fi_all.xlsx
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.027569847127042725 +/- 0.0044044480116614305</t>
+          <t>-0.027727991565629974 +/- 0.004505189376746767</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>-0.009857670005271468 +/- 0.0023580673955029127</t>
+          <t>-0.009804955192409048 +/- 0.002348029251588842</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2691,74 +2691,74 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>0.0011673151750972721 +/- 0.0012342974261137622</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.04002918287937742 +/- 0.006492962950873927</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-0.009046692607003859 +/- 0.004207690419043209</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-0.009046692607003859 +/- 0.004207690419043209</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.006809338521400754 +/- 0.0015835428595427673</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.017607003891050597 +/- 0.004483158996810502</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.03764591439688714 +/- 0.005175792060086763</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.018725680933852174 +/- 0.002829803153266328</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0.027772373540856043 +/- 0.0046420759387890125</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.016439688715953315 +/- 0.005322709735527055</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.2853112840466926 +/- 0.008530967570104526</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>-0.010165369649805411 +/- 0.0030018043043208986</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.27120622568093383 +/- 0.009213556718110607</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>0.0011186770428015524 +/- 0.0012504825031305832</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.04002918287937742 +/- 0.006492962950873927</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-0.009046692607003859 +/- 0.004207690419043209</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-0.009046692607003859 +/- 0.004207690419043209</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0.006809338521400754 +/- 0.0015835428595427673</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0.017607003891050597 +/- 0.004483158996810502</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0.03764591439688714 +/- 0.005175792060086763</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0.018725680933852174 +/- 0.002829803153266328</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0.027772373540856043 +/- 0.0046420759387890125</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0.016439688715953315 +/- 0.005322709735527055</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0.2853112840466926 +/- 0.008530967570104526</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>-0.010165369649805411 +/- 0.0030018043043208986</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>0.27120622568093383 +/- 0.009213556718110607</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0.0011186770428015524 +/- 0.0012504825031305832</t>
-        </is>
-      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>0.004620622568093369 +/- 0.002444035900078029</t>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.02660505836575877 +/- 0.005693155195405394</t>
+          <t>0.02655642023346305 +/- 0.005660442228006266</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-0.03127147766323023 +/- 0.0038782523318605846</t>
+          <t>-0.03132056946489935 +/- 0.003980978877312385</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.011493123772102154 +/- 0.0032297214583052337</t>
+          <t>-0.01154223968565814 +/- 0.0032598317300678074</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.028388998035363478 +/- 0.0022270695577121173</t>
+          <t>0.02833988212180749 +/- 0.0022513097517418207</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.0014333492594362008 +/- 0.0038756425782461995</t>
+          <t>-0.0013855709507883285 +/- 0.003959839010987759</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>-0.011657907310081206 +/- 0.002712865660120098</t>
+          <t>-0.011562350692785462 +/- 0.00278429092868294</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.0015766841853798396 +/- 0.0006773744328121474</t>
+          <t>0.0015289058767319562 +/- 0.0006688963210702526</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00014485755673587786 +/- 0.0006845701052031854</t>
+          <t>0.00019314340898116678 +/- 0.0006896599158419031</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
